--- a/sources/julia_step3.xlsx
+++ b/sources/julia_step3.xlsx
@@ -422,8 +422,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
@@ -459,12 +459,12 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="C98" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">

--- a/sources/julia_step3.xlsx
+++ b/sources/julia_step3.xlsx
@@ -816,6 +816,11 @@
           <t>Special Tag Throw with Michelle only. Michelle finishes with a Lariat. Total damage is 12,24.</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1b569aeb-dd63-4db9-bfe2-caa3a868a11d</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>1b569aeb-dd63-4db9-bfe2-caa3a868a11d</t>
@@ -853,6 +858,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>48718773-f00b-471d-8dc4-830794a42ebc</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
           <t>48718773-f00b-471d-8dc4-830794a42ebc</t>
@@ -890,6 +900,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>35dc67c0-d4fa-495c-aefc-39f34e65507b</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>35dc67c0-d4fa-495c-aefc-39f34e65507b</t>
@@ -925,6 +940,11 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>b70b8f8a-633b-40a2-8811-5f4191813631</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5370,6 +5390,11 @@
           <t>hmmhLmhhLm</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>f26af970-57e3-45d4-baba-6711c2809508</t>
+        </is>
+      </c>
       <c r="O103" t="inlineStr">
         <is>
           <t>f26af970-57e3-45d4-baba-6711c2809508</t>
@@ -5397,6 +5422,11 @@
           <t>hmmhLmmLm!</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>8ba99c8f-7b6d-46d5-860f-492405778df4</t>
+        </is>
+      </c>
       <c r="O104" t="inlineStr">
         <is>
           <t>8ba99c8f-7b6d-46d5-860f-492405778df4</t>
@@ -5422,6 +5452,11 @@
       <c r="I105" t="inlineStr">
         <is>
           <t>hmmhLmmmLm</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>12d35c24-0209-43bc-a4fa-a6173fd493c0</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
